--- a/光伏配储项目/电价数据/2026/珠山站.xlsx
+++ b/光伏配储项目/电价数据/2026/珠山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5105</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.42235</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45437</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12226</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09944</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09801</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12186</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07169</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.13476</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.17272</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15255</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.07507</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10387</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.03537</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17298</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22504</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22545</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10803</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.01171</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.19129</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19757</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6518699999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.46679</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.52855</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.16079</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6306499999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.48245</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.46818</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5738300000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46247</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.61934</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8104</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64319</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63126</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.76475</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.01281</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6755099999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.74859</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.64285</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6140599999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47325</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42588</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69868</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.90632</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.68144</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.28899</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6944400000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52742</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51878</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5052300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50861</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48899</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49973</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5956699999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.69497</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51455</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.20192</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.44046</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.15014</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5412899999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.80333</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.50804</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12626</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49511</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42528</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5885499999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.71933</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5722</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.69348</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.75827</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.6749299999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.58646</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5406299999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.53769</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.51108</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.76959</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66242</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46393</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33462</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.62072</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.78262</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.65615</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.5286900000000001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.47637</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.47544</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.96575</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.67841</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.7094400000000001</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20852</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.11168</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26811</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47362</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.51454</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48346</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.15923</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45868</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52152</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54016</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62002</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.62934</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61399</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47595</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50022</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44277</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44964</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34243</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45957</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.19859</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.21642</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.22814</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.53928</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.5541200000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.12068</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07989</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.23039</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.68986</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06363000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24119</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24605</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21575</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13652</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.27393</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.59611</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29856</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.10246</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04423</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.10061</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.11181</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04441</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04603</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.07448</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04676</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03506</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04238</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04251</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04468</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05156</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.03921</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04717</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.21073</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.11223</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.15873</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35093</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.73837</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04690999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04171</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10362</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00175</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04407</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04519</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20013</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33569</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31794</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17256</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17113</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15877</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15649</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62205</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92044</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91625</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86876</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8935299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63271</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19303</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8717200000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5457000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33691</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0371</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5368200000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7960700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7781</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7816000000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87654</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49793</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40609</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45542</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21319</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87909</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55118</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62799</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53988</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42502</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45281</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58665</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5960700000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6022999999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66784</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58088</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8797</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63289</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9259400000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.90799</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8635</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35345</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9238200000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46687</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47647</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50014</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.23427</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16554</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26233</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1992</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19814</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89034</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.14907</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.98968</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.63439</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.53026</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.42602</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41371</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46505</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46263</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.96577</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56775</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25225</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5747100000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.9883</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6371599999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25919</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57577</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.44158</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68855</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43731</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32405</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.94229</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.18316</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18737</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19306</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.04044</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.01486</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17152</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.17927</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.17144</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.18394</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.20942</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.20699</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.15364</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.09704</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.20948</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.17794</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18217</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.25084</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.27066</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42397</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34885</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49912</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19924</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24079</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.23761</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35452</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.05482</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.16591</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25916</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.18205</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6623</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.43284</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28682</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.41777</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34957</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.70245</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31911</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20006</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28447</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14785</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.51602</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.53108</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.67713</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45539</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48836</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.48939</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6448700000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16405</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42557</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48487</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.48071</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.46319</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.13688</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80838</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5209600000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.47571</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6003200000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.54667</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47555</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.38648</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50818</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15433</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46375</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11324</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36544</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22743</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23051</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25024</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13993</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25113</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16998</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18225</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22889</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26464</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23296</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35017</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17081</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00069</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02696</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01372</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03932</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01565</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03672</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02493</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02639</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00098</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03222999999999999</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17832</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20229</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.15488</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.59941</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18175</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25746</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27454</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23225</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25342</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23766</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.17872</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.66164</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.65801</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.67443</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.60681</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10813</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24373</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.19161</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.13591</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10041</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23198</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12576</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04257</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.06383</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18411</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02413</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13506</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14244</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.15949</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.11792</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12692</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.12674</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16011</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25672</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32349</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.03063</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14107</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.31393</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.53128</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.24088</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33982</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.48822</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48708</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.46282</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34716</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17634</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06578000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.18062</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03358</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16181</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05374</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07102</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07833</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05777</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17633</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15062</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17075</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34621</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.54547</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26403</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11526</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01539</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04096</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16871</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03702</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.005679999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01862</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01358</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04497</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.16592</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41537</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36994</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23678</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14766</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21373</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24111</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11773</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15587</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.03079</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.007650000000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04707</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04725</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04433</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04149</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08064</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02856</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06428</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09914000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17689</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20303</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12435</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12757</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15223</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19254</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21043</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37868</v>
       </c>
     </row>
   </sheetData>
